--- a/quizzes/021_executive_functioning_quiz--quizzes.xlsx
+++ b/quizzes/021_executive_functioning_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>self_regulate</t>
+          <t>planning_and_organization</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Self Regulate</t>
+          <t>Planning and Organization</t>
         </is>
       </c>
     </row>
@@ -1471,131 +1471,131 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>planning_and_organization</t>
+          <t>task_planning</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Planning and Organization</t>
+          <t>Task Planning</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_choices</t>
+          <t>quiz_answers_1_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>task_planning</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Task Planning</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_choices</t>
+          <t>quiz_answers_1_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sustained_attention</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sustained Attention</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_choices</t>
+          <t>quiz_answers_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>quiz_answers_1_choices</t>
+          <t>quiz_answers_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>quiz_answers_1_choices</t>
+          <t>executive_functioning_domain_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>cognitive_flexibility</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Cognitive Flexibility</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>quiz_answers_2_choices</t>
+          <t>executive_functioning_domain_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>planning_and_problem_solving</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Planning and Problem Solving</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>quiz_answers_2_choices</t>
+          <t>executive_functioning_domain_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sustained_attention</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sustained Attention</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>cognitive_flexibility</t>
+          <t>initiation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cognitive Flexibility</t>
+          <t>Initiation</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>planning_and_problem_solving</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Planning and Problem Solving</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sustained_attention</t>
+          <t>task_initiation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sustained Attention</t>
+          <t>Task Initiation</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>initiation</t>
+          <t>emotional_regulation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Emotional Regulation</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>self_monitoring</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Self Monitoring</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>task_initiation</t>
+          <t>working_memory</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Task Initiation</t>
+          <t>Working Memory</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>emotional_regulation</t>
+          <t>self_control</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Emotional Regulation</t>
+          <t>Self Control</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>self_monitoring</t>
+          <t>self_motivation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Self Monitoring</t>
+          <t>Self Motivation</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>working_memory</t>
+          <t>task_monitoring</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Working Memory</t>
+          <t>Task Monitoring</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>self_control</t>
+          <t>multitasking</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Self Control</t>
+          <t>Multitasking</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>self_motivation</t>
+          <t>self_regulate</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Self Motivation</t>
+          <t>Self Regulate</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>task_monitoring</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Task Monitoring</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>multitasking</t>
+          <t>attention_to_details</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Multitasking</t>
+          <t>Attention to Details</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>self_regulate</t>
+          <t>goal_setting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Self Regulate</t>
+          <t>Goal Setting</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Planning</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>attention_to_details</t>
+          <t>organization_of_task</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Attention to Details</t>
+          <t>Organization of Task</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>goal_setting</t>
+          <t>planning_and_organization</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Planning and Organization</t>
         </is>
       </c>
     </row>
@@ -1896,87 +1896,87 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>task_planning</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Task Planning</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_2_choices</t>
+          <t>quiz_answers_3_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>organization_of_task</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Organization of Task</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_2_choices</t>
+          <t>quiz_answers_3_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>self_regulate</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Self Regulate</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_2_choices</t>
+          <t>executive_functioning_domain_3_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>planning_and_organization</t>
+          <t>cognitive_flexibility</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Planning and Organization</t>
+          <t>Cognitive Flexibility</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_2_choices</t>
+          <t>executive_functioning_domain_3_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>task_planning</t>
+          <t>planning_and_problem_solving</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Task Planning</t>
+          <t>Planning and Problem Solving</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_2_choices</t>
+          <t>executive_functioning_domain_3_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1993,51 +1993,51 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_2_choices</t>
+          <t>executive_functioning_domain_3_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>initiation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Initiation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>quiz_answers_3_choices</t>
+          <t>executive_functioning_domain_3_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>quiz_answers_3_choices</t>
+          <t>executive_functioning_domain_3_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>task_initiation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Task Initiation</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>cognitive_flexibility</t>
+          <t>emotional_regulation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cognitive Flexibility</t>
+          <t>Emotional Regulation</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>planning_and_problem_solving</t>
+          <t>self_monitoring</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Planning and Problem Solving</t>
+          <t>Self Monitoring</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sustained_attention</t>
+          <t>working_memory</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sustained Attention</t>
+          <t>Working Memory</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>initiation</t>
+          <t>self_control</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Self Control</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>self_motivation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Self Motivation</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>task_initiation</t>
+          <t>task_monitoring</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Task Initiation</t>
+          <t>Task Monitoring</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>emotional_regulation</t>
+          <t>multitasking</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Emotional Regulation</t>
+          <t>Multitasking</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>self_monitoring</t>
+          <t>self_regulate</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Self Monitoring</t>
+          <t>Self Regulate</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>working_memory</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Working Memory</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>self_control</t>
+          <t>attention_to_details</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Self Control</t>
+          <t>Attention to Details</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>self_motivation</t>
+          <t>goal_setting</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Self Motivation</t>
+          <t>Goal Setting</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>task_monitoring</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Task Monitoring</t>
+          <t>Planning</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>multitasking</t>
+          <t>organization_of_task</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Multitasking</t>
+          <t>Organization of Task</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>self_regulate</t>
+          <t>planning_and_organization</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Self Regulate</t>
+          <t>Planning and Organization</t>
         </is>
       </c>
     </row>
@@ -2287,233 +2287,233 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>task_planning</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Task Planning</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_3_choices</t>
+          <t>quiz_answers_4_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>attention_to_details</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Attention to Details</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_3_choices</t>
+          <t>quiz_answers_4_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>goal_setting</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_3_choices</t>
+          <t>quiz_answers_5_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_3_choices</t>
+          <t>quiz_answers_5_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>organization_of_task</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Organization of Task</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_3_choices</t>
+          <t>executive_functioning_domain_4_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>self_regulate</t>
+          <t>cognitive_flexibility</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Self Regulate</t>
+          <t>Cognitive Flexibility</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_3_choices</t>
+          <t>executive_functioning_domain_4_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>planning_and_organization</t>
+          <t>planning_and_problem_solving</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Planning and Organization</t>
+          <t>Planning and Problem Solving</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_3_choices</t>
+          <t>executive_functioning_domain_4_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>task_planning</t>
+          <t>sustained_attention</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Task Planning</t>
+          <t>Sustained Attention</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_3_choices</t>
+          <t>executive_functioning_domain_4_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>sustained_attention</t>
+          <t>initiation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sustained Attention</t>
+          <t>Initiation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_3_choices</t>
+          <t>executive_functioning_domain_4_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>quiz_answers_4_choices</t>
+          <t>executive_functioning_domain_4_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>task_initiation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Task Initiation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>quiz_answers_4_choices</t>
+          <t>executive_functioning_domain_4_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>emotional_regulation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Emotional Regulation</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>quiz_answers_5_choices</t>
+          <t>executive_functioning_domain_4_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>self_monitoring</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Self Monitoring</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>quiz_answers_5_choices</t>
+          <t>executive_functioning_domain_4_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>working_memory</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Working Memory</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>cognitive_flexibility</t>
+          <t>self_control</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cognitive Flexibility</t>
+          <t>Self Control</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>planning_and_problem_solving</t>
+          <t>self_motivation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Planning and Problem Solving</t>
+          <t>Self Motivation</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>sustained_attention</t>
+          <t>task_monitoring</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sustained Attention</t>
+          <t>Task Monitoring</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>initiation</t>
+          <t>multitasking</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Multitasking</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>self_regulate</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Self Regulate</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>task_initiation</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Task Initiation</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>emotional_regulation</t>
+          <t>attention_to_details</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Emotional Regulation</t>
+          <t>Attention to Details</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>self_monitoring</t>
+          <t>goal_setting</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Self Monitoring</t>
+          <t>Goal Setting</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>working_memory</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Working Memory</t>
+          <t>Planning</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>self_control</t>
+          <t>organization_of_task</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Self Control</t>
+          <t>Organization of Task</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>self_motivation</t>
+          <t>planning_and_organization</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Self Motivation</t>
+          <t>Planning and Organization</t>
         </is>
       </c>
     </row>
@@ -2712,250 +2712,250 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>task_monitoring</t>
+          <t>task_planning</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Task Monitoring</t>
+          <t>Task Planning</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>quiz_answers_6_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>multitasking</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Multitasking</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>quiz_answers_6_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>self_regulate</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Self Regulate</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>cognitive_flexibility</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Cognitive Flexibility</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>attention_to_details</t>
+          <t>planning_and_problem_solving</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Attention to Details</t>
+          <t>Planning and Problem Solving</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>goal_setting</t>
+          <t>sustained_attention</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Sustained Attention</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>initiation</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Initiation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>organization_of_task</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Organization of Task</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>self_regulate</t>
+          <t>task_initiation</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Self Regulate</t>
+          <t>Task Initiation</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>planning_and_organization</t>
+          <t>emotional_regulation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Planning and Organization</t>
+          <t>Emotional Regulation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>task_planning</t>
+          <t>self_monitoring</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Task Planning</t>
+          <t>Self Monitoring</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>sustained_attention</t>
+          <t>working_memory</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sustained Attention</t>
+          <t>Working Memory</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_4_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>self_control</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Self Control</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>quiz_answers_6_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>self_motivation</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Self Motivation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>quiz_answers_6_choices</t>
+          <t>executive_functioning_domain_5_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>task_monitoring</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Task Monitoring</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>cognitive_flexibility</t>
+          <t>multitasking</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cognitive Flexibility</t>
+          <t>Multitasking</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>planning_and_problem_solving</t>
+          <t>self_regulate</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Planning and Problem Solving</t>
+          <t>Self Regulate</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>sustained_attention</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sustained Attention</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>initiation</t>
+          <t>attention_to_details</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Attention to Details</t>
         </is>
       </c>
     </row>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>goal_setting</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Goal Setting</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>task_initiation</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Task Initiation</t>
+          <t>Planning</t>
         </is>
       </c>
     </row>
@@ -3069,12 +3069,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>emotional_regulation</t>
+          <t>organization_of_task</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Emotional Regulation</t>
+          <t>Organization of Task</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>self_monitoring</t>
+          <t>planning_and_organization</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Self Monitoring</t>
+          <t>Planning and Organization</t>
         </is>
       </c>
     </row>
@@ -3103,301 +3103,301 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>working_memory</t>
+          <t>task_planning</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Working Memory</t>
+          <t>Task Planning</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>quiz_answers_7_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>self_control</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Self Control</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>quiz_answers_7_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>self_motivation</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Self Motivation</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>task_monitoring</t>
+          <t>cognitive_flexibility</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Task Monitoring</t>
+          <t>Cognitive Flexibility</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>multitasking</t>
+          <t>planning_and_problem_solving</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Multitasking</t>
+          <t>Planning and Problem Solving</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>self_regulate</t>
+          <t>sustained_attention</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Self Regulate</t>
+          <t>Sustained Attention</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>initiation</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Initiation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>attention_to_details</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Attention to Details</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>goal_setting</t>
+          <t>task_initiation</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Task Initiation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>emotional_regulation</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Emotional Regulation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>organization_of_task</t>
+          <t>self_monitoring</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Organization of Task</t>
+          <t>Self Monitoring</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>self_regulate</t>
+          <t>working_memory</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Self Regulate</t>
+          <t>Working Memory</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>planning_and_organization</t>
+          <t>self_control</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Planning and Organization</t>
+          <t>Self Control</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>task_planning</t>
+          <t>self_motivation</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Task Planning</t>
+          <t>Self Motivation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>sustained_attention</t>
+          <t>task_monitoring</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sustained Attention</t>
+          <t>Task Monitoring</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>executive_functioning_domain_5_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>multitasking</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Multitasking</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>quiz_answers_7_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>self_regulate</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Self Regulate</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>quiz_answers_7_choices</t>
+          <t>executive_functioning_domain_6_choices</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>cognitive_flexibility</t>
+          <t>attention_to_details</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cognitive Flexibility</t>
+          <t>Attention to Details</t>
         </is>
       </c>
     </row>
@@ -3426,12 +3426,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>planning_and_problem_solving</t>
+          <t>goal_setting</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Planning and Problem Solving</t>
+          <t>Goal Setting</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>sustained_attention</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Sustained Attention</t>
+          <t>Planning</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>initiation</t>
+          <t>organization_of_task</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Organization of Task</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>planning_and_organization</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Planning and Organization</t>
         </is>
       </c>
     </row>
@@ -3494,318 +3494,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>task_initiation</t>
+          <t>task_planning</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Task Initiation</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>emotional_regulation</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Emotional Regulation</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>self_monitoring</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Self Monitoring</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>working_memory</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Working Memory</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>self_control</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Self Control</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>self_motivation</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Self Motivation</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>task_monitoring</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Task Monitoring</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>multitasking</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Multitasking</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>self_regulate</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Self Regulate</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>time_management</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Time Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>attention_to_details</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Attention to Details</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>goal_setting</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>planning</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>organization_of_task</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Organization of Task</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>self_regulate</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Self Regulate</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>planning_and_organization</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Planning and Organization</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>task_planning</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
           <t>Task Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>sustained_attention</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Sustained Attention</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>executive_functioning_domain_6_choices</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>time_management</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Time Management</t>
         </is>
       </c>
     </row>
